--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484665_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484665_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.4491</v>
+        <v>7.1879</v>
       </c>
       <c r="E2" t="n">
-        <v>7.2309</v>
+        <v>6.2422</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2181</v>
+        <v>0.9456</v>
       </c>
       <c r="G2" t="n">
         <v>6.1427</v>
@@ -610,13 +610,13 @@
         <v>0.9163</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7987</v>
+        <v>0.5375</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6094</v>
+        <v>0.6207</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1893</v>
+        <v>-0.0832</v>
       </c>
       <c r="V2" t="n">
         <v>2.5235</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.185</v>
+        <v>5.0884</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9581</v>
+        <v>4.1094</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2268</v>
+        <v>0.9791</v>
       </c>
       <c r="G3" t="n">
         <v>5.6622</v>
@@ -688,13 +688,13 @@
         <v>0.3665</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0166</v>
+        <v>-0.1131</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3854</v>
+        <v>-0.2342</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3688</v>
+        <v>0.121</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6439</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2594</v>
+        <v>2.625</v>
       </c>
       <c r="E4" t="n">
-        <v>1.945</v>
+        <v>1.2858</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3144</v>
+        <v>1.3392</v>
       </c>
       <c r="G4" t="n">
         <v>2.0595</v>
@@ -766,13 +766,13 @@
         <v>0.733</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4381</v>
+        <v>-0.1963</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6946</v>
+        <v>0.0355</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2565</v>
+        <v>-0.2317</v>
       </c>
       <c r="V4" t="n">
         <v>0.945</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. HERNANDEZ BENACHES</t>
+          <t>F. BLASCO MANZANO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.253</v>
+        <v>1.7941</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1942</v>
+        <v>-0.7094</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.9412</v>
+        <v>2.5035</v>
       </c>
       <c r="G5" t="n">
-        <v>2.932</v>
+        <v>4.933</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.8765</v>
+        <v>3.574</v>
       </c>
       <c r="I5" t="n">
-        <v>4.8085</v>
+        <v>1.359</v>
       </c>
       <c r="J5" t="n">
-        <v>4.3872</v>
+        <v>3.5278</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.4154</v>
+        <v>3.2262</v>
       </c>
       <c r="L5" t="n">
-        <v>5.8026</v>
+        <v>0.3016</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4552</v>
+        <v>1.4053</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4611</v>
+        <v>0.3478</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9941</v>
+        <v>1.0575</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3665</v>
+        <v>-4.3982</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9163</v>
+        <v>-5.681</v>
       </c>
       <c r="R5" t="n">
         <v>1.2828</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0901</v>
+        <v>-0.0077</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2767</v>
+        <v>0.1769</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8134</v>
+        <v>-0.1846</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9554</v>
+        <v>1.267</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.9554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. BLASCO MANZANO</t>
+          <t>S. HERNANDEZ BENACHES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7825</v>
+        <v>1.3497</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.5476</v>
+        <v>3.167</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3301</v>
+        <v>-1.8173</v>
       </c>
       <c r="G6" t="n">
-        <v>4.933</v>
+        <v>2.932</v>
       </c>
       <c r="H6" t="n">
-        <v>3.574</v>
+        <v>-1.8765</v>
       </c>
       <c r="I6" t="n">
-        <v>1.359</v>
+        <v>4.8085</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5278</v>
+        <v>4.3872</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2262</v>
+        <v>-1.4154</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3016</v>
+        <v>5.8026</v>
       </c>
       <c r="M6" t="n">
-        <v>1.4053</v>
+        <v>-1.4552</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3478</v>
+        <v>-0.4611</v>
       </c>
       <c r="O6" t="n">
-        <v>1.0575</v>
+        <v>-0.9941</v>
       </c>
       <c r="P6" t="n">
-        <v>-4.3982</v>
+        <v>0.3665</v>
       </c>
       <c r="Q6" t="n">
-        <v>-5.681</v>
+        <v>-0.9163</v>
       </c>
       <c r="R6" t="n">
         <v>1.2828</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0194</v>
+        <v>-0.9933999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6614</v>
+        <v>-0.3039</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.358</v>
+        <v>-0.6895</v>
       </c>
       <c r="V6" t="n">
-        <v>1.267</v>
+        <v>-0.9554</v>
       </c>
       <c r="W6" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6506</v>
+        <v>-0.2165</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3224</v>
+        <v>-0.9378</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6718</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>-1.2334</v>
@@ -1000,13 +1000,13 @@
         <v>0.5498</v>
       </c>
       <c r="S7" t="n">
-        <v>0.033</v>
+        <v>0.4672</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1471</v>
+        <v>0.2376</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1801</v>
+        <v>0.2296</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. PINA RODRIGUEZ</t>
+          <t>R. CARRION BALLESTER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2182</v>
+        <v>-0.844</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7845</v>
+        <v>-0.845</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4337</v>
+        <v>0.001</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8682</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5797</v>
+        <v>0.018</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2885</v>
+        <v>0.6922</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6194</v>
+        <v>0.4985</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6194</v>
+        <v>0.2227</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.2758</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2489</v>
+        <v>0.2118</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0397</v>
+        <v>-0.2047</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2885</v>
+        <v>0.4164</v>
       </c>
       <c r="P8" t="n">
         <v>0.1833</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.0995</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1833</v>
+        <v>1.2828</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5333</v>
+        <v>-0.7821</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1652</v>
+        <v>-0.244</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3681</v>
+        <v>-0.5381</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. CARRION BALLESTER</t>
+          <t>E. PINA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2481</v>
+        <v>-1.0973</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2986</v>
+        <v>-0.6884</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0506</v>
+        <v>-0.4089</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7102000000000001</v>
+        <v>-0.8682</v>
       </c>
       <c r="H9" t="n">
-        <v>0.018</v>
+        <v>-0.5797</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6922</v>
+        <v>-0.2885</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4985</v>
+        <v>-0.6194</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2227</v>
+        <v>-0.6194</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2758</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2118</v>
+        <v>-0.2489</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2047</v>
+        <v>0.0397</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4164</v>
+        <v>-0.2885</v>
       </c>
       <c r="P9" t="n">
         <v>0.1833</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0995</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2828</v>
+        <v>0.1833</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1861</v>
+        <v>-0.4123</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6976</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4886</v>
+        <v>-0.3433</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9554</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.9554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3819</v>
+        <v>-1.7633</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.553</v>
+        <v>-2.0583</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1711</v>
+        <v>0.295</v>
       </c>
       <c r="G10" t="n">
         <v>-4.6319</v>
@@ -1234,13 +1234,13 @@
         <v>1.2828</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6505</v>
+        <v>-0.0319</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4962</v>
+        <v>-0.0015</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1542</v>
+        <v>-0.0304</v>
       </c>
       <c r="V10" t="n">
         <v>2.5339</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9973</v>
+        <v>-2.9012</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.2058</v>
+        <v>-4.1097</v>
       </c>
       <c r="F11" t="n">
         <v>1.2085</v>
@@ -1312,10 +1312,10 @@
         <v>1.2828</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1094</v>
+        <v>-0.0132</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2368</v>
+        <v>0.333</v>
       </c>
       <c r="U11" t="n">
         <v>-0.3462</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.9985</v>
+        <v>-5.6876</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3244</v>
+        <v>-3.0631</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.6741</v>
+        <v>-2.6245</v>
       </c>
       <c r="G12" t="n">
         <v>-2.9055</v>
@@ -1390,13 +1390,13 @@
         <v>0.9163</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2317</v>
+        <v>-0.9208</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6425</v>
+        <v>-0.3812</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5891</v>
+        <v>-0.5396</v>
       </c>
       <c r="V12" t="n">
         <v>-0.945</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.4344</v>
+        <v>5.5352</v>
       </c>
       <c r="E13" t="n">
-        <v>1.291899999999999</v>
+        <v>2.3927</v>
       </c>
       <c r="F13" t="n">
-        <v>3.142399999999999</v>
+        <v>3.142500000000001</v>
       </c>
       <c r="G13" t="n">
         <v>10.0513</v>
@@ -1456,7 +1456,7 @@
         <v>-0.9171</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1577000000000005</v>
+        <v>0.1577000000000003</v>
       </c>
       <c r="P13" t="n">
         <v>-5.497599999999999</v>
@@ -1468,19 +1468,19 @@
         <v>10.0792</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.5673</v>
+        <v>-2.4661</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9313</v>
+        <v>0.1699000000000002</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.6359</v>
+        <v>-2.636</v>
       </c>
       <c r="V13" t="n">
         <v>3.4478</v>
       </c>
       <c r="W13" t="n">
-        <v>6.989</v>
+        <v>6.989000000000001</v>
       </c>
       <c r="X13" t="n">
         <v>-3.5414</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7901</v>
+        <v>3.4034</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0456</v>
+        <v>1.5263</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7445</v>
+        <v>1.8771</v>
       </c>
       <c r="G14" t="n">
         <v>0.7258</v>
@@ -1546,13 +1546,13 @@
         <v>2.0158</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4121</v>
+        <v>0.2012</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4419</v>
+        <v>0.0389</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0298</v>
+        <v>0.1623</v>
       </c>
       <c r="V14" t="n">
         <v>0.6439</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. DOMINGUEZ ALEIXANDRE</t>
+          <t>J. MARTINEZ TEJERO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6821</v>
+        <v>2.2414</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4206</v>
+        <v>0.0017</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7385</v>
+        <v>2.2397</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.0031</v>
+        <v>-0.7067</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.7688</v>
+        <v>-0.896</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.2343</v>
+        <v>0.1893</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5725</v>
+        <v>-1.0805</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1399</v>
+        <v>-0.5327</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.4327</v>
+        <v>-0.5478</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.4306</v>
+        <v>0.3738</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.629</v>
+        <v>-0.3633</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8017</v>
+        <v>0.7371</v>
       </c>
       <c r="P15" t="n">
-        <v>1.2828</v>
+        <v>1.6493</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1833</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4661</v>
+        <v>1.6493</v>
       </c>
       <c r="S15" t="n">
-        <v>4.0255</v>
+        <v>0.0319</v>
       </c>
       <c r="T15" t="n">
-        <v>3.5325</v>
+        <v>-0.1847</v>
       </c>
       <c r="U15" t="n">
-        <v>0.493</v>
+        <v>0.2166</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6231</v>
+        <v>1.267</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6439</v>
+        <v>1.267</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MARTINEZ TEJERO</t>
+          <t>M. ANTONI RODRIGUEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7243</v>
+        <v>1.2873</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3829</v>
+        <v>-0.7095</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1071</v>
+        <v>1.9968</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7067</v>
+        <v>0.541</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.896</v>
+        <v>0.2623</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1893</v>
+        <v>0.2787</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.0805</v>
+        <v>0.3827</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5327</v>
+        <v>-0.4092</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5478</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3738</v>
+        <v>0.1584</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3633</v>
+        <v>0.6715</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7371</v>
+        <v>-0.5131</v>
       </c>
       <c r="P16" t="n">
-        <v>1.6493</v>
+        <v>0.1833</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.0995</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6493</v>
+        <v>1.2828</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4853</v>
+        <v>1.1861</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5694</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.5556</v>
       </c>
       <c r="V16" t="n">
-        <v>1.267</v>
+        <v>-0.6231</v>
       </c>
       <c r="W16" t="n">
-        <v>1.267</v>
+        <v>-0.6231</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. ANTONI RODRIGUEZ</t>
+          <t>S. DOMINGUEZ ALEIXANDRE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0993</v>
+        <v>0.4006</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5172</v>
+        <v>1.209</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6165</v>
+        <v>-0.8085</v>
       </c>
       <c r="G17" t="n">
-        <v>0.541</v>
+        <v>-2.0031</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2623</v>
+        <v>-0.7688</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2787</v>
+        <v>-1.2343</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3827</v>
+        <v>-0.5725</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.4092</v>
+        <v>-0.1399</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7917999999999999</v>
+        <v>-0.4327</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1584</v>
+        <v>-1.4306</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6715</v>
+        <v>-0.629</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5131</v>
+        <v>-0.8017</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1833</v>
+        <v>1.2828</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0995</v>
+        <v>-0.1833</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2828</v>
+        <v>1.4661</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9981</v>
+        <v>1.744</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8228</v>
+        <v>1.3209</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1753</v>
+        <v>0.4231</v>
       </c>
       <c r="V17" t="n">
         <v>-0.6231</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.6231</v>
+        <v>0.6439</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.181</v>
+        <v>0.2168</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3355</v>
+        <v>2.4316</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.5165</v>
+        <v>-2.2148</v>
       </c>
       <c r="G18" t="n">
         <v>0.7357</v>
@@ -1858,13 +1858,13 @@
         <v>1.0995</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2061</v>
+        <v>0.6039</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2217</v>
+        <v>-0.1255</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4278</v>
+        <v>0.7294</v>
       </c>
       <c r="V18" t="n">
         <v>-2.2224</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-0.255</v>
       </c>
       <c r="E19" t="n">
         <v>-0.3574</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2983</v>
+        <v>0.1024</v>
       </c>
       <c r="G19" t="n">
         <v>-1.4567</v>
@@ -1936,13 +1936,13 @@
         <v>1.8326</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3877</v>
+        <v>0.013</v>
       </c>
       <c r="T19" t="n">
         <v>-0.0565</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3312</v>
+        <v>0.0696</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6439</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. FOS CERVERA</t>
+          <t>J. ARNAIZ VEGA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9392</v>
+        <v>-1.2037</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8266</v>
+        <v>0.3222</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1126</v>
+        <v>-1.5259</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1711</v>
+        <v>-2.0618</v>
       </c>
       <c r="H20" t="n">
-        <v>0.09180000000000001</v>
+        <v>-0.2638</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.263</v>
+        <v>-1.7981</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7435</v>
+        <v>1.2525</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4552</v>
+        <v>0.5819</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.1987</v>
+        <v>0.6706</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4276</v>
+        <v>-3.3143</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3633</v>
+        <v>-0.8457</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0643</v>
+        <v>-2.4686</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3665</v>
+        <v>-0.733</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0995</v>
+        <v>-2.0158</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4661</v>
+        <v>1.2828</v>
       </c>
       <c r="S20" t="n">
-        <v>0.177</v>
+        <v>0.6358</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6946</v>
+        <v>0.1301</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5175999999999999</v>
+        <v>0.5056</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3115</v>
+        <v>0.9554</v>
       </c>
       <c r="W20" t="n">
-        <v>0.3219</v>
+        <v>0.9554</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. ARNAIZ VEGA</t>
+          <t>B. FOS CERVERA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2351</v>
+        <v>-1.4097</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9278</v>
+        <v>-1.4996</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3073</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.0618</v>
+        <v>-1.1711</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2638</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.7981</v>
+        <v>-1.263</v>
       </c>
       <c r="J21" t="n">
-        <v>1.2525</v>
+        <v>-0.7435</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5819</v>
+        <v>0.4552</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6706</v>
+        <v>-1.1987</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.3143</v>
+        <v>-0.4276</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8457</v>
+        <v>-0.3633</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.4686</v>
+        <v>-0.0643</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.733</v>
+        <v>0.3665</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0158</v>
+        <v>-1.0995</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2828</v>
+        <v>1.4661</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3956</v>
+        <v>-0.2935</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1199</v>
+        <v>0.0215</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7243000000000001</v>
+        <v>-0.3151</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9554</v>
+        <v>-0.3115</v>
       </c>
       <c r="W21" t="n">
-        <v>0.9554</v>
+        <v>0.3219</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. MERENCIO FERRER</t>
+          <t>S. ARNAIZ VEGA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6335</v>
+        <v>-1.4576</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3792</v>
+        <v>0.4811</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2543</v>
+        <v>-1.9387</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.6074</v>
+        <v>1.0197</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.7192</v>
+        <v>2.9943</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8882</v>
+        <v>-1.9746</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.0578</v>
+        <v>2.8733</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.0995</v>
+        <v>2.796</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0417</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5496</v>
+        <v>-1.8535</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6198</v>
+        <v>0.1983</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-2.0519</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1833</v>
+        <v>-2.0158</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.2828</v>
+        <v>-3.1154</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4661</v>
+        <v>1.0995</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4137</v>
+        <v>0.8054</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5845</v>
+        <v>0.4012</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1708</v>
+        <v>0.4042</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6231</v>
+        <v>-1.267</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6231</v>
+        <v>0.3219</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. ARNAIZ VEGA</t>
+          <t>J. MERENCIO FERRER</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.037</v>
+        <v>-2.7501</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6728</v>
+        <v>-2.4753</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.3642</v>
+        <v>-0.2748</v>
       </c>
       <c r="G23" t="n">
-        <v>1.0197</v>
+        <v>-2.6074</v>
       </c>
       <c r="H23" t="n">
-        <v>2.9943</v>
+        <v>-1.7192</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.9746</v>
+        <v>-0.8882</v>
       </c>
       <c r="J23" t="n">
-        <v>2.8733</v>
+        <v>-1.0578</v>
       </c>
       <c r="K23" t="n">
-        <v>2.796</v>
+        <v>-1.0995</v>
       </c>
       <c r="L23" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.0417</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.8535</v>
+        <v>-1.5496</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1983</v>
+        <v>-0.6198</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.0519</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.0158</v>
+        <v>0.1833</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.1154</v>
+        <v>-1.2828</v>
       </c>
       <c r="R23" t="n">
-        <v>1.0995</v>
+        <v>1.4661</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7739</v>
+        <v>0.2971</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7526</v>
+        <v>0.4883</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0213</v>
+        <v>-0.1912</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.267</v>
+        <v>-0.6231</v>
       </c>
       <c r="W23" t="n">
-        <v>0.3219</v>
+        <v>-0.6231</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.5889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.0485</v>
+        <v>-2.9844</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.8802</v>
+        <v>-4.0725</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8317</v>
+        <v>1.0881</v>
       </c>
       <c r="G24" t="n">
         <v>-3.0666</v>
@@ -2326,13 +2326,13 @@
         <v>0.9163</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2014</v>
+        <v>0.2655</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1637</v>
+        <v>-0.0286</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0377</v>
+        <v>0.2941</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.434200000000001</v>
+        <v>-2.511000000000001</v>
       </c>
       <c r="E25" t="n">
         <v>-3.1424</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.2919</v>
+        <v>0.6312999999999995</v>
       </c>
       <c r="G25" t="n">
         <v>-10.0512</v>
@@ -2377,7 +2377,7 @@
         <v>-8.174199999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7595000000000001</v>
+        <v>0.7594999999999992</v>
       </c>
       <c r="K25" t="n">
         <v>0.9168999999999998</v>
@@ -2395,7 +2395,7 @@
         <v>-8.0167</v>
       </c>
       <c r="P25" t="n">
-        <v>5.497800000000001</v>
+        <v>5.4978</v>
       </c>
       <c r="Q25" t="n">
         <v>-10.0791</v>
@@ -2404,13 +2404,13 @@
         <v>15.5769</v>
       </c>
       <c r="S25" t="n">
-        <v>3.5672</v>
+        <v>5.4904</v>
       </c>
       <c r="T25" t="n">
         <v>2.6361</v>
       </c>
       <c r="U25" t="n">
-        <v>0.9311</v>
+        <v>2.8542</v>
       </c>
       <c r="V25" t="n">
         <v>-3.4478</v>
